--- a/tests/data/QuoteData.xlsx
+++ b/tests/data/QuoteData.xlsx
@@ -4,19 +4,23 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22188" windowHeight="9000"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22188" windowHeight="9000" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Create" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Update" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Search" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Cancel" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="SpotRate" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Convert" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Pricing" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>TestCase</t>
   </si>
@@ -73,6 +77,54 @@
   </si>
   <si>
     <t>Quotation Created</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>CancelQuote</t>
+  </si>
+  <si>
+    <t>Change of specification</t>
+  </si>
+  <si>
+    <t>Automation cancel</t>
+  </si>
+  <si>
+    <t>SpotRate</t>
+  </si>
+  <si>
+    <t>SpotRateQuote</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>FlightNo</t>
+  </si>
+  <si>
+    <t>ConvertBooking</t>
+  </si>
+  <si>
+    <t>AA0221</t>
+  </si>
+  <si>
+    <t>AddCode</t>
+  </si>
+  <si>
+    <t>DeleteCode</t>
+  </si>
+  <si>
+    <t>PricingAddDelete</t>
+  </si>
+  <si>
+    <t>DGR</t>
+  </si>
+  <si>
+    <t>TRU</t>
   </si>
 </sst>
 </file>
@@ -557,22 +609,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -592,16 +644,154 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="2" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="2" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="2" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <cols>
+    <col min="1" max="2" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>700</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
+    <col min="1" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -609,21 +799,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/tests/data/QuoteData.xlsx
+++ b/tests/data/QuoteData.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22188" windowHeight="9000" activeTab="4"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Create" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Update" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Search" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Cancel" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="SpotRate" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Convert" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Pricing" state="visible" r:id="rId10"/>
+    <sheet name="Create" sheetId="1" r:id="rId1"/>
+    <sheet name="Update" sheetId="2" r:id="rId2"/>
+    <sheet name="Search" sheetId="3" r:id="rId3"/>
+    <sheet name="Cancel" sheetId="4" r:id="rId4"/>
+    <sheet name="SpotRate" sheetId="5" r:id="rId5"/>
+    <sheet name="Convert" sheetId="6" r:id="rId6"/>
+    <sheet name="Pricing" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
   <si>
     <t>TestCase</t>
   </si>
@@ -61,6 +74,15 @@
     <t>AUTO-QUOTE</t>
   </si>
   <si>
+    <t>CreateQuote_AC</t>
+  </si>
+  <si>
+    <t>Air Canada</t>
+  </si>
+  <si>
+    <t>YUL</t>
+  </si>
+  <si>
     <t>UpdateQuote</t>
   </si>
   <si>
@@ -88,6 +110,9 @@
     <t>CancelQuote</t>
   </si>
   <si>
+    <t>MIA</t>
+  </si>
+  <si>
     <t>Change of specification</t>
   </si>
   <si>
@@ -100,16 +125,16 @@
     <t>SpotRateQuote</t>
   </si>
   <si>
-    <t>MIA</t>
-  </si>
-  <si>
     <t>FlightNo</t>
   </si>
   <si>
     <t>ConvertBooking</t>
   </si>
   <si>
-    <t>AA0221</t>
+    <t>PHL</t>
+  </si>
+  <si>
+    <t>AA0203</t>
   </si>
   <si>
     <t>AddCode</t>
@@ -130,46 +155,386 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -192,30 +557,315 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -541,14 +1191,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="7" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +1225,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="28.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="28.8" customHeight="1" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -597,24 +1248,52 @@
         <v>620</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" customHeight="1" spans="1:8">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>226</v>
+      </c>
+      <c r="G3" s="2">
+        <v>226</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="3" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -628,9 +1307,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="1" spans="1:4">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -644,180 +1323,240 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="2" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="2" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="21.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="1" spans="1:6">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>156</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="2" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="1" spans="1:5">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>700</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>27</v>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="1" spans="1:5">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>31</v>
+      <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <headerFooter/>
 </worksheet>
 </file>